--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.34110164392558</v>
+        <v>2.492929017137907</v>
       </c>
       <c r="D2" t="n">
-        <v>14.62250377777851</v>
+        <v>2.376156863889008</v>
       </c>
       <c r="E2" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F2" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.64728204027124</v>
+        <v>3.192683331544076</v>
       </c>
       <c r="D3" t="n">
-        <v>18.91329770425437</v>
+        <v>3.073410876941335</v>
       </c>
       <c r="E3" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F3" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.943363569468783</v>
+        <v>0.9657965800386773</v>
       </c>
       <c r="D4" t="n">
-        <v>4.972879020365042</v>
+        <v>0.8080928408093193</v>
       </c>
       <c r="E4" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F4" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.47769836615977</v>
+        <v>3.815125984500962</v>
       </c>
       <c r="D5" t="n">
-        <v>23.4379121017131</v>
+        <v>3.808660716528379</v>
       </c>
       <c r="E5" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F5" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.89327247917733</v>
+        <v>7.620156777866317</v>
       </c>
       <c r="D6" t="n">
-        <v>17.83214897846253</v>
+        <v>2.897724209000162</v>
       </c>
       <c r="E6" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F6" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.63877801134853</v>
+        <v>9.366301426844137</v>
       </c>
       <c r="D7" t="n">
-        <v>19.06172011004566</v>
+        <v>3.097529517882419</v>
       </c>
       <c r="E7" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F7" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.94774930208243</v>
+        <v>2.591509261588395</v>
       </c>
       <c r="D8" t="n">
-        <v>16.86660112784908</v>
+        <v>2.740822683275475</v>
       </c>
       <c r="E8" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F8" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.36384219506255</v>
+        <v>5.746624356697665</v>
       </c>
       <c r="D9" t="n">
-        <v>18.37171820608769</v>
+        <v>2.985404208489249</v>
       </c>
       <c r="E9" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F9" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>93.21066750957903</v>
+        <v>15.14673347030659</v>
       </c>
       <c r="D10" t="n">
-        <v>70.80849574731101</v>
+        <v>11.50638055893804</v>
       </c>
       <c r="E10" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F10" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.0634447661404</v>
+        <v>4.235309774497815</v>
       </c>
       <c r="D11" t="n">
-        <v>26.83862861726237</v>
+        <v>4.361277150305136</v>
       </c>
       <c r="E11" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F11" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>49.56663922178197</v>
+        <v>8.054578873539571</v>
       </c>
       <c r="D12" t="n">
-        <v>35.04651572500197</v>
+        <v>5.695058805312819</v>
       </c>
       <c r="E12" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F12" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>63.12961522263575</v>
+        <v>10.25856247367831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.21746251094979</v>
+        <v>7.347837658029341</v>
       </c>
       <c r="E13" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F13" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>47.24578964123534</v>
+        <v>7.677440816700743</v>
       </c>
       <c r="D14" t="n">
-        <v>38.19319837478383</v>
+        <v>6.206394735902372</v>
       </c>
       <c r="E14" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F14" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>56.54973191454255</v>
+        <v>9.189331436113164</v>
       </c>
       <c r="D15" t="n">
-        <v>40.65836072175073</v>
+        <v>6.606983617284493</v>
       </c>
       <c r="E15" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F15" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>26.07122873826803</v>
+        <v>4.236574669968555</v>
       </c>
       <c r="D16" t="n">
-        <v>23.23367639888842</v>
+        <v>3.775472414819368</v>
       </c>
       <c r="E16" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F16" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>24.75219031714396</v>
+        <v>4.022230926535893</v>
       </c>
       <c r="D17" t="n">
-        <v>27.26609767907077</v>
+        <v>4.430740872849</v>
       </c>
       <c r="E17" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F17" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>27.51355479483163</v>
+        <v>4.47095265416014</v>
       </c>
       <c r="D18" t="n">
-        <v>32.25824585213094</v>
+        <v>5.241964950971278</v>
       </c>
       <c r="E18" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F18" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>23.76024592565954</v>
+        <v>3.861039962919675</v>
       </c>
       <c r="D19" t="n">
-        <v>29.44350959881571</v>
+        <v>4.784570309807553</v>
       </c>
       <c r="E19" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F19" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>49.24684234854476</v>
+        <v>8.002611881638524</v>
       </c>
       <c r="D20" t="n">
-        <v>26.48628112715917</v>
+        <v>4.304020683163366</v>
       </c>
       <c r="E20" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F20" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>8.13173594668995</v>
+        <v>1.321407091337117</v>
       </c>
       <c r="D21" t="n">
-        <v>12.29463053439608</v>
+        <v>1.997877461839364</v>
       </c>
       <c r="E21" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F21" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>8.634433700209412</v>
+        <v>1.40309547628403</v>
       </c>
       <c r="D22" t="n">
-        <v>7.437315223846684</v>
+        <v>1.208563723875086</v>
       </c>
       <c r="E22" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F22" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>44.46713583182817</v>
+        <v>7.225909572672078</v>
       </c>
       <c r="D23" t="n">
-        <v>12.79387304231535</v>
+        <v>2.079004369376244</v>
       </c>
       <c r="E23" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F23" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>14.22916000188893</v>
+        <v>2.312238500306952</v>
       </c>
       <c r="D24" t="n">
-        <v>20.63931289588604</v>
+        <v>3.353888345581481</v>
       </c>
       <c r="E24" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F24" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>4.561973570655678</v>
+        <v>0.7413207052315478</v>
       </c>
       <c r="D25" t="n">
-        <v>3.363287990567499</v>
+        <v>0.5465342984672186</v>
       </c>
       <c r="E25" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F25" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>22.36817204153422</v>
+        <v>3.634827956749311</v>
       </c>
       <c r="D26" t="n">
-        <v>16.85702378880843</v>
+        <v>2.739266365681369</v>
       </c>
       <c r="E26" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F26" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>28.98984437723253</v>
+        <v>4.710849711300287</v>
       </c>
       <c r="D27" t="n">
-        <v>10.21450918682505</v>
+        <v>1.65985774285907</v>
       </c>
       <c r="E27" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F27" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>18.43227690419872</v>
+        <v>2.995244996932293</v>
       </c>
       <c r="D28" t="n">
-        <v>22.17948679995773</v>
+        <v>3.60416660499313</v>
       </c>
       <c r="E28" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F28" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>41.14995677325937</v>
+        <v>6.686867975654648</v>
       </c>
       <c r="D29" t="n">
-        <v>35.07680398340476</v>
+        <v>5.699980647303273</v>
       </c>
       <c r="E29" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F29" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>35.16680858546287</v>
+        <v>5.714606395137717</v>
       </c>
       <c r="D30" t="n">
-        <v>11.75187242348206</v>
+        <v>1.909679268815835</v>
       </c>
       <c r="E30" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F30" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>77.20260366886347</v>
+        <v>12.54542309619032</v>
       </c>
       <c r="D31" t="n">
-        <v>38.19257048779112</v>
+        <v>6.206292704266057</v>
       </c>
       <c r="E31" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F31" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>48.3896507255913</v>
+        <v>7.863318242908587</v>
       </c>
       <c r="D32" t="n">
-        <v>43.88794314063932</v>
+        <v>7.13179076035389</v>
       </c>
       <c r="E32" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F32" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>36.06561465868573</v>
+        <v>5.860662382036431</v>
       </c>
       <c r="D33" t="n">
-        <v>34.31154724250989</v>
+        <v>5.575626426907857</v>
       </c>
       <c r="E33" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F33" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>90.25940207259224</v>
+        <v>14.66715283679624</v>
       </c>
       <c r="D34" t="n">
-        <v>52.08375182965934</v>
+        <v>8.463609672319643</v>
       </c>
       <c r="E34" t="n">
-        <v>22.4500893263923</v>
+        <v>3.648139515538749</v>
       </c>
       <c r="F34" t="n">
-        <v>14.42400692098521</v>
+        <v>2.343901124660098</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
